--- a/tests/e2e/content-import/fixtures/u09_03_lessons_broken.xlsx
+++ b/tests/e2e/content-import/fixtures/u09_03_lessons_broken.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>lesson_code</t>
   </si>
@@ -37,22 +37,34 @@
     <t>sort_order</t>
   </si>
   <si>
+    <t>e2e-u9-les-01</t>
+  </si>
+  <si>
+    <t>e2e-u9-sub</t>
+  </si>
+  <si>
+    <t>e2e-u9-unit</t>
+  </si>
+  <si>
+    <t>درس الحزمة الأول</t>
+  </si>
+  <si>
+    <t>12 دقيقة</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>e2e-u9-les-broken</t>
   </si>
   <si>
-    <t>e2e-u9-sub</t>
-  </si>
-  <si>
-    <t>e2e-u9-unit-missing</t>
-  </si>
-  <si>
-    <t>درس بمرجع وحدة مفقودة</t>
+    <t>e2e-u9-sub-missing</t>
+  </si>
+  <si>
+    <t>درس بمرجع مادة مفقودة</t>
   </si>
   <si>
     <t>5 دقائق</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
 </sst>
 </file>
@@ -429,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -481,6 +493,32 @@
         <v>13</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3">
         <v>9</v>
       </c>
     </row>
